--- a/TestData/Vayahvikas.xlsx
+++ b/TestData/Vayahvikas.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">testNameDetails</t>
   </si>
@@ -34,6 +34,12 @@
     <t xml:space="preserve">mobilenumber</t>
   </si>
   <si>
+    <t xml:space="preserve">post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
     <t xml:space="preserve">validate login feature for valid credicnticals </t>
   </si>
   <si>
@@ -41,6 +47,12 @@
   </si>
   <si>
     <t xml:space="preserve">Regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testpost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing</t>
   </si>
 </sst>
 </file>
@@ -160,11 +172,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="12.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -180,19 +193,31 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>9361288067</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
